--- a/baseline_models/eemdijk_runs.xlsx
+++ b/baseline_models/eemdijk_runs.xlsx
@@ -509,22 +509,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,55 +542,65 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>layer_s1</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>layer_s2</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>active_model</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>gamma_dry</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>gamma_wet</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Su_S</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Su_m</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>MC_phi</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>MC_c</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>MC_psi</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>su_table_key</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Layers</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>POP</t>
         </is>
@@ -605,24 +617,29 @@
           <t>0b_Ophoogzand,_phi</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L 15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>17</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>19.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>40</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -637,24 +654,29 @@
           <t>0a_Afdekklei,_cphi</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L 14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>17</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>30</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -671,19 +693,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>L 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>20</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>45</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -700,27 +732,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>L 6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L 6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>12.6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>12.6</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>0.37</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.9</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>SP 1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
@@ -739,29 +781,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>L 9, L 10, L 11, L 8, L 7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>L 10, L 9, L 11, L 8, L 7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>13.2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>13.2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>0.47</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.9</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SP 5, SP 2, SP 4, SP 3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>20.0, 20.0, 40.0, 20.0</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SP 5, SP 2, SP 9, SP 4, SP 3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>20.0, 20.0, 20.0, 40.0, 20.0</t>
         </is>
       </c>
     </row>
@@ -778,19 +830,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>L 12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L 12, L 13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>14.4</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>14.4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>30</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -807,29 +869,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>L 5, L 4, L 2, L 3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>L 5, L 4, L 2, L 3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>10.2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>10.2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>0.55</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>0.9</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SP 8, SP 6, SP 7</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>15.0, 15.0, 40.0</t>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SP 8, SP 7, SP 6, SP 10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>15.0, 40.0, 15.0, 15.0</t>
         </is>
       </c>
     </row>

--- a/baseline_models/eemdijk_runs.xlsx
+++ b/baseline_models/eemdijk_runs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-6030" windowWidth="16440" windowHeight="28320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3900" yWindow="345" windowWidth="12150" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" state="visible" r:id="rId1"/>
@@ -22627,14 +22627,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-18 11:15:42</t>
+          <t>2026-05-28 12:09:56</t>
         </is>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1.006616753784954</v>
+        <v>1.013563492815955</v>
       </c>
     </row>
     <row r="3">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-18 11:15:47</t>
+          <t>2026-05-28 12:10:03</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -22673,14 +22673,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-18 11:15:51</t>
+          <t>2026-05-28 12:10:07</t>
         </is>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.901558998824988</v>
+        <v>0.9036493935760458</v>
       </c>
     </row>
     <row r="5">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-18 11:15:56</t>
+          <t>2026-05-28 12:10:14</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -22719,14 +22719,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:00</t>
+          <t>2026-05-28 12:10:19</t>
         </is>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8320194120803064</v>
+        <v>0.8372073171965905</v>
       </c>
     </row>
     <row r="7">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:06</t>
+          <t>2026-05-28 12:10:27</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -22765,14 +22765,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:09</t>
+          <t>2026-05-28 12:10:32</t>
         </is>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.090575732473364</v>
+        <v>1.107251443925093</v>
       </c>
     </row>
     <row r="9">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:13</t>
+          <t>2026-05-28 12:10:38</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -22811,14 +22811,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:17</t>
+          <t>2026-05-28 12:10:43</t>
         </is>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1.132866187328283</v>
+        <v>1.148552089970685</v>
       </c>
     </row>
     <row r="11">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:21</t>
+          <t>2026-05-28 12:10:49</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -22857,14 +22857,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:25</t>
+          <t>2026-05-28 12:10:54</t>
         </is>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.418744051937515</v>
+        <v>1.422937471036207</v>
       </c>
     </row>
     <row r="13">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:30</t>
+          <t>2026-05-28 12:11:01</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -22903,14 +22903,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:33</t>
+          <t>2026-05-28 12:11:06</t>
         </is>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.478032574811326</v>
+        <v>1.481661101927221</v>
       </c>
     </row>
     <row r="15">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:38</t>
+          <t>2026-05-28 12:11:12</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -22949,14 +22949,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:41</t>
+          <t>2026-05-28 12:11:20</t>
         </is>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8625798064251216</v>
+        <v>0.8702261626154925</v>
       </c>
     </row>
     <row r="17">
@@ -22972,7 +22972,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:46</t>
+          <t>2026-05-28 12:11:26</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -22995,14 +22995,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:49</t>
+          <t>2026-05-28 12:11:31</t>
         </is>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8517092470516548</v>
+        <v>0.8513333412433851</v>
       </c>
     </row>
     <row r="19">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:54</t>
+          <t>2026-05-28 12:11:37</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -23041,14 +23041,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-05-18 11:16:57</t>
+          <t>2026-05-28 12:11:41</t>
         </is>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7714996262966958</v>
+        <v>0.7760298796711206</v>
       </c>
     </row>
     <row r="21">
@@ -23064,7 +23064,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:02</t>
+          <t>2026-05-28 12:11:47</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -23087,14 +23087,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:06</t>
+          <t>2026-05-28 12:11:51</t>
         </is>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7630727145337286</v>
+        <v>0.7667200961145376</v>
       </c>
     </row>
     <row r="23">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:11</t>
+          <t>2026-05-28 12:11:58</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -23133,14 +23133,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:15</t>
+          <t>2026-05-28 12:12:03</t>
         </is>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7103739912737073</v>
+        <v>0.7158635196913866</v>
       </c>
     </row>
     <row r="25">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:20</t>
+          <t>2026-05-28 12:12:09</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -23179,14 +23179,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:23</t>
+          <t>2026-05-28 12:12:13</t>
         </is>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6983569441607532</v>
+        <v>0.705629569739905</v>
       </c>
     </row>
     <row r="27">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:28</t>
+          <t>2026-05-28 12:12:19</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -23225,14 +23225,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:35</t>
+          <t>2026-05-28 12:12:27</t>
         </is>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5521392501635047</v>
+        <v>0.5657012802939486</v>
       </c>
     </row>
     <row r="29">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:40</t>
+          <t>2026-05-28 12:12:34</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -23271,14 +23271,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:46</t>
+          <t>2026-05-28 12:12:42</t>
         </is>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5521392501635047</v>
+        <v>0.5657012802939486</v>
       </c>
     </row>
     <row r="31">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:55</t>
+          <t>2026-05-28 12:12:52</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -23317,14 +23317,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-05-18 11:17:58</t>
+          <t>2026-05-28 12:12:56</t>
         </is>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4901834304963467</v>
+        <v>0.4862284032871856</v>
       </c>
     </row>
     <row r="33">
@@ -23340,7 +23340,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:03</t>
+          <t>2026-05-28 12:13:02</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -23363,14 +23363,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:07</t>
+          <t>2026-05-28 12:13:06</t>
         </is>
       </c>
       <c r="D34" t="b">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4901834304963467</v>
+        <v>0.4862284032871856</v>
       </c>
     </row>
     <row r="35">
@@ -23386,7 +23386,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:11</t>
+          <t>2026-05-28 12:13:12</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -23409,14 +23409,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:15</t>
+          <t>2026-05-28 12:13:16</t>
         </is>
       </c>
       <c r="D36" t="b">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4382764537789158</v>
+        <v>0.4625478248857945</v>
       </c>
     </row>
     <row r="37">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:20</t>
+          <t>2026-05-28 12:13:23</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -23455,14 +23455,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:24</t>
+          <t>2026-05-28 12:13:27</t>
         </is>
       </c>
       <c r="D38" t="b">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4583550153840417</v>
+        <v>0.4625478248857945</v>
       </c>
     </row>
     <row r="39">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:30</t>
+          <t>2026-05-28 12:13:34</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -23501,14 +23501,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:33</t>
+          <t>2026-05-28 12:13:39</t>
         </is>
       </c>
       <c r="D40" t="b">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8366952485327197</v>
+        <v>0.8379510585659931</v>
       </c>
     </row>
     <row r="41">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:37</t>
+          <t>2026-05-28 12:13:45</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -23547,14 +23547,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:41</t>
+          <t>2026-05-28 12:13:50</t>
         </is>
       </c>
       <c r="D42" t="b">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8366952485327197</v>
+        <v>0.8379510585659931</v>
       </c>
     </row>
     <row r="43">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:45</t>
+          <t>2026-05-28 12:13:56</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -23593,14 +23593,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:49</t>
+          <t>2026-05-28 12:14:01</t>
         </is>
       </c>
       <c r="D44" t="b">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.876765643599923</v>
+        <v>0.8780876031964937</v>
       </c>
     </row>
     <row r="45">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:53</t>
+          <t>2026-05-28 12:14:06</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -23639,14 +23639,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-18 11:18:57</t>
+          <t>2026-05-28 12:14:10</t>
         </is>
       </c>
       <c r="D46" t="b">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.876765643599923</v>
+        <v>0.8780876031964937</v>
       </c>
     </row>
     <row r="47">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:01</t>
+          <t>2026-05-28 12:14:17</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:04</t>
+          <t>2026-05-28 12:14:22</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:09</t>
+          <t>2026-05-28 12:14:29</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -23731,7 +23731,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:12</t>
+          <t>2026-05-28 12:14:35</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:17</t>
+          <t>2026-05-28 12:14:41</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -23777,14 +23777,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:21</t>
+          <t>2026-05-28 12:14:46</t>
         </is>
       </c>
       <c r="D52" t="b">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1.195292116572891</v>
+        <v>1.195293911757535</v>
       </c>
     </row>
     <row r="53">
@@ -23800,7 +23800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:25</t>
+          <t>2026-05-28 12:14:52</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -23823,14 +23823,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:29</t>
+          <t>2026-05-28 12:14:56</t>
         </is>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1.195292116572891</v>
+        <v>1.195293911757535</v>
       </c>
     </row>
     <row r="55">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:33</t>
+          <t>2026-05-28 12:15:02</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -23869,14 +23869,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:38</t>
+          <t>2026-05-28 12:15:07</t>
         </is>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9324071510959394</v>
+        <v>0.9425547795987308</v>
       </c>
     </row>
     <row r="57">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:47</t>
+          <t>2026-05-28 12:15:17</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -23915,14 +23915,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:51</t>
+          <t>2026-05-28 12:15:21</t>
         </is>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9324071510959394</v>
+        <v>0.9425547795987308</v>
       </c>
     </row>
     <row r="59">
@@ -23938,7 +23938,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:56</t>
+          <t>2026-05-28 12:15:29</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -23961,14 +23961,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-18 11:19:59</t>
+          <t>2026-05-28 12:15:34</t>
         </is>
       </c>
       <c r="D60" t="b">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8123508364417782</v>
+        <v>0.8262874896305181</v>
       </c>
     </row>
     <row r="61">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:04</t>
+          <t>2026-05-28 12:15:41</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -24007,14 +24007,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:08</t>
+          <t>2026-05-28 12:15:46</t>
         </is>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8123508364417782</v>
+        <v>0.8262874896305181</v>
       </c>
     </row>
     <row r="63">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:13</t>
+          <t>2026-05-28 12:15:53</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -24053,14 +24053,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:16</t>
+          <t>2026-05-28 12:15:57</t>
         </is>
       </c>
       <c r="D64" t="b">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7557877189353936</v>
+        <v>0.761807303483963</v>
       </c>
     </row>
     <row r="65">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:21</t>
+          <t>2026-05-28 12:16:02</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -24099,14 +24099,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:25</t>
+          <t>2026-05-28 12:16:06</t>
         </is>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7557877189353936</v>
+        <v>0.761807303483963</v>
       </c>
     </row>
     <row r="67">
@@ -24122,7 +24122,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:30</t>
+          <t>2026-05-28 12:16:11</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -24145,14 +24145,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:34</t>
+          <t>2026-05-28 12:16:15</t>
         </is>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.030777736779656</v>
+        <v>1.05217042347542</v>
       </c>
     </row>
     <row r="69">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:38</t>
+          <t>2026-05-28 12:16:20</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -24191,14 +24191,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:42</t>
+          <t>2026-05-28 12:16:24</t>
         </is>
       </c>
       <c r="D70" t="b">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1.030777736779656</v>
+        <v>1.05217042347542</v>
       </c>
     </row>
     <row r="71">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:46</t>
+          <t>2026-05-28 12:16:29</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -24237,14 +24237,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:50</t>
+          <t>2026-05-28 12:16:33</t>
         </is>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1.065593863356487</v>
+        <v>1.094844054352498</v>
       </c>
     </row>
     <row r="73">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:54</t>
+          <t>2026-05-28 12:16:37</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -24283,14 +24283,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-05-18 11:20:58</t>
+          <t>2026-05-28 12:16:41</t>
         </is>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.065593863356487</v>
+        <v>1.094844054352498</v>
       </c>
     </row>
     <row r="75">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:02</t>
+          <t>2026-05-28 12:16:46</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -24329,14 +24329,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:05</t>
+          <t>2026-05-28 12:16:50</t>
         </is>
       </c>
       <c r="D76" t="b">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1.345885152845065</v>
+        <v>1.37285342009722</v>
       </c>
     </row>
     <row r="77">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:10</t>
+          <t>2026-05-28 12:16:55</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -24375,14 +24375,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:13</t>
+          <t>2026-05-28 12:16:59</t>
         </is>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>1.345885152845065</v>
+        <v>1.37285342009722</v>
       </c>
     </row>
     <row r="79">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:18</t>
+          <t>2026-05-28 12:17:04</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -24421,14 +24421,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:21</t>
+          <t>2026-05-28 12:17:08</t>
         </is>
       </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.406665005207664</v>
+        <v>1.432636914078867</v>
       </c>
     </row>
     <row r="81">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:25</t>
+          <t>2026-05-28 12:17:13</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -24467,14 +24467,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:29</t>
+          <t>2026-05-28 12:17:17</t>
         </is>
       </c>
       <c r="D82" t="b">
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>1.406665005207664</v>
+        <v>1.432636914078867</v>
       </c>
     </row>
     <row r="83">
@@ -24490,7 +24490,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:34</t>
+          <t>2026-05-28 12:17:22</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -24513,14 +24513,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-05-27 16:22:33</t>
+          <t>2026-05-28 12:17:26</t>
         </is>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9125359861587387</v>
+        <v>0.9240669472875673</v>
       </c>
     </row>
     <row r="85">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-05-27 16:22:38</t>
+          <t>2026-05-28 12:17:31</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -24559,14 +24559,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-05-27 16:22:42</t>
+          <t>2026-05-28 12:17:34</t>
         </is>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9125359861587387</v>
+        <v>0.9240669472875673</v>
       </c>
     </row>
     <row r="87">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-05-27 16:22:50</t>
+          <t>2026-05-28 12:17:42</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -24605,14 +24605,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-05-27 16:22:54</t>
+          <t>2026-05-28 12:17:46</t>
         </is>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7922597093001859</v>
+        <v>0.8080789902100437</v>
       </c>
     </row>
     <row r="89">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:00</t>
+          <t>2026-05-28 12:17:51</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -24651,14 +24651,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:03</t>
+          <t>2026-05-28 12:17:55</t>
         </is>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7922597093001859</v>
+        <v>0.8080789902100437</v>
       </c>
     </row>
     <row r="91">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:09</t>
+          <t>2026-05-28 12:18:00</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -24697,14 +24697,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:12</t>
+          <t>2026-05-28 12:18:04</t>
         </is>
       </c>
       <c r="D92" t="b">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7370972333100204</v>
+        <v>0.7429672823203297</v>
       </c>
     </row>
     <row r="93">
@@ -24720,7 +24720,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:17</t>
+          <t>2026-05-28 12:18:09</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -24743,14 +24743,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:21</t>
+          <t>2026-05-28 12:18:13</t>
         </is>
       </c>
       <c r="D94" t="b">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7370972333100204</v>
+        <v>0.7429672823203297</v>
       </c>
     </row>
     <row r="95">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:26</t>
+          <t>2026-05-28 12:18:17</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -24789,14 +24789,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:30</t>
+          <t>2026-05-28 12:18:21</t>
         </is>
       </c>
       <c r="D96" t="b">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1.016913132424626</v>
+        <v>1.033415776631785</v>
       </c>
     </row>
     <row r="97">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:34</t>
+          <t>2026-05-28 12:18:26</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -24835,14 +24835,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:38</t>
+          <t>2026-05-28 12:18:30</t>
         </is>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>1.016913132424626</v>
+        <v>1.033415776631785</v>
       </c>
     </row>
     <row r="99">
@@ -24858,7 +24858,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:42</t>
+          <t>2026-05-28 12:18:34</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -24881,14 +24881,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:46</t>
+          <t>2026-05-28 12:18:38</t>
         </is>
       </c>
       <c r="D100" t="b">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>1.051338898790744</v>
+        <v>1.074484608428134</v>
       </c>
     </row>
     <row r="101">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:51</t>
+          <t>2026-05-28 12:18:43</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -24927,14 +24927,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-05-27 16:23:55</t>
+          <t>2026-05-28 12:18:47</t>
         </is>
       </c>
       <c r="D102" t="b">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>1.051338898790744</v>
+        <v>1.074484608428134</v>
       </c>
     </row>
     <row r="103">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:00</t>
+          <t>2026-05-28 12:18:51</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -24973,14 +24973,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:04</t>
+          <t>2026-05-28 12:18:55</t>
         </is>
       </c>
       <c r="D104" t="b">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>1.330189401463143</v>
+        <v>1.360635869836691</v>
       </c>
     </row>
     <row r="105">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:09</t>
+          <t>2026-05-28 12:19:00</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -25019,14 +25019,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:12</t>
+          <t>2026-05-28 12:19:05</t>
         </is>
       </c>
       <c r="D106" t="b">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1.330189401463143</v>
+        <v>1.360635869836691</v>
       </c>
     </row>
     <row r="107">
@@ -25042,7 +25042,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:17</t>
+          <t>2026-05-28 12:19:09</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -25065,14 +25065,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:20</t>
+          <t>2026-05-28 12:19:13</t>
         </is>
       </c>
       <c r="D108" t="b">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>1.391248506720316</v>
+        <v>1.418199733693432</v>
       </c>
     </row>
     <row r="109">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:28</t>
+          <t>2026-05-28 12:19:21</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -25111,14 +25111,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:31</t>
+          <t>2026-05-28 12:19:25</t>
         </is>
       </c>
       <c r="D110" t="b">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>1.391248506720316</v>
+        <v>1.418199733693432</v>
       </c>
     </row>
     <row r="111">
@@ -25134,7 +25134,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:36</t>
+          <t>2026-05-28 12:19:30</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -25157,14 +25157,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:39</t>
+          <t>2026-05-28 12:19:34</t>
         </is>
       </c>
       <c r="D112" t="b">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8889031376321467</v>
+        <v>0.8991397628615401</v>
       </c>
     </row>
     <row r="113">
@@ -25180,7 +25180,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:47</t>
+          <t>2026-05-28 12:19:42</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -25203,14 +25203,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:51</t>
+          <t>2026-05-28 12:19:45</t>
         </is>
       </c>
       <c r="D114" t="b">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8889031376321467</v>
+        <v>0.8991397628615401</v>
       </c>
     </row>
     <row r="115">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:55</t>
+          <t>2026-05-28 12:19:50</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -25249,14 +25249,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-05-27 16:24:59</t>
+          <t>2026-05-28 12:19:54</t>
         </is>
       </c>
       <c r="D116" t="b">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7646439727988269</v>
+        <v>0.7820998876701274</v>
       </c>
     </row>
     <row r="117">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:04</t>
+          <t>2026-05-28 12:19:59</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -25295,14 +25295,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:07</t>
+          <t>2026-05-28 12:20:03</t>
         </is>
       </c>
       <c r="D118" t="b">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7646439727988269</v>
+        <v>0.7820998876701274</v>
       </c>
     </row>
     <row r="119">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:12</t>
+          <t>2026-05-28 12:20:07</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -25341,14 +25341,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:16</t>
+          <t>2026-05-28 12:20:11</t>
         </is>
       </c>
       <c r="D120" t="b">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7031845369652042</v>
+        <v>0.7190944784028969</v>
       </c>
     </row>
     <row r="121">
@@ -25364,7 +25364,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:21</t>
+          <t>2026-05-28 12:20:16</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -25387,14 +25387,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:25</t>
+          <t>2026-05-28 12:20:20</t>
         </is>
       </c>
       <c r="D122" t="b">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7031845369652042</v>
+        <v>0.7190944784028969</v>
       </c>
     </row>
     <row r="123">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:30</t>
+          <t>2026-05-28 12:20:25</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -25433,14 +25433,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:34</t>
+          <t>2026-05-28 12:20:29</t>
         </is>
       </c>
       <c r="D124" t="b">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9964538567920108</v>
+        <v>1.014692165536887</v>
       </c>
     </row>
     <row r="125">
@@ -25456,7 +25456,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:38</t>
+          <t>2026-05-28 12:20:33</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -25479,14 +25479,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:42</t>
+          <t>2026-05-28 12:20:37</t>
         </is>
       </c>
       <c r="D126" t="b">
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0.9964538567920108</v>
+        <v>1.014692165536887</v>
       </c>
     </row>
     <row r="127">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:46</t>
+          <t>2026-05-28 12:20:41</t>
         </is>
       </c>
       <c r="D127" t="b">
@@ -25525,14 +25525,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:50</t>
+          <t>2026-05-28 12:20:45</t>
         </is>
       </c>
       <c r="D128" t="b">
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>1.06522687894448</v>
+        <v>1.056122774083748</v>
       </c>
     </row>
     <row r="129">
@@ -25548,7 +25548,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:54</t>
+          <t>2026-05-28 12:20:50</t>
         </is>
       </c>
       <c r="D129" t="b">
@@ -25571,14 +25571,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-05-27 16:25:58</t>
+          <t>2026-05-28 12:20:54</t>
         </is>
       </c>
       <c r="D130" t="b">
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1.06522687894448</v>
+        <v>1.056122774083748</v>
       </c>
     </row>
     <row r="131">
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:03</t>
+          <t>2026-05-28 12:20:58</t>
         </is>
       </c>
       <c r="D131" t="b">
@@ -25617,14 +25617,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:06</t>
+          <t>2026-05-28 12:21:02</t>
         </is>
       </c>
       <c r="D132" t="b">
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>1.306259881816145</v>
+        <v>1.342981199152263</v>
       </c>
     </row>
     <row r="133">
@@ -25640,7 +25640,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:14</t>
+          <t>2026-05-28 12:21:10</t>
         </is>
       </c>
       <c r="D133" t="b">
@@ -25663,14 +25663,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:18</t>
+          <t>2026-05-28 12:21:17</t>
         </is>
       </c>
       <c r="D134" t="b">
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>1.306259881816145</v>
+        <v>1.342981199152263</v>
       </c>
     </row>
     <row r="135">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:23</t>
+          <t>2026-05-28 12:21:23</t>
         </is>
       </c>
       <c r="D135" t="b">
@@ -25709,14 +25709,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:26</t>
+          <t>2026-05-28 12:21:27</t>
         </is>
       </c>
       <c r="D136" t="b">
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>1.370648606740945</v>
+        <v>1.400544636899432</v>
       </c>
     </row>
     <row r="137">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:34</t>
+          <t>2026-05-28 12:21:37</t>
         </is>
       </c>
       <c r="D137" t="b">
@@ -25755,14 +25755,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:38</t>
+          <t>2026-05-28 12:21:41</t>
         </is>
       </c>
       <c r="D138" t="b">
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>1.370648606740945</v>
+        <v>1.400544636899432</v>
       </c>
     </row>
     <row r="139">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:45</t>
+          <t>2026-05-28 12:21:51</t>
         </is>
       </c>
       <c r="D139" t="b">
